--- a/paper_tables/Table_1c_Material_Categories.xlsx
+++ b/paper_tables/Table_1c_Material_Categories.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Material_Categories" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Material Categories" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
@@ -506,7 +506,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Mean Ef (eV/at)</t>
+          <t>Mean Ef (eV/atom)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
